--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DBA0E4-5FAC-43B9-BE72-FDCAEA05FADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32128F88-0986-4A39-BCC5-5A863A5F8FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E752C8B-AE93-4C4A-8F61-A51C643EC55B}"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2E752C8B-AE93-4C4A-8F61-A51C643EC55B}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster" sheetId="1" r:id="rId1"/>
     <sheet name="Train" sheetId="2" r:id="rId2"/>
-    <sheet name="Stage" sheetId="3" r:id="rId3"/>
+    <sheet name="Turret_Train" sheetId="5" r:id="rId3"/>
+    <sheet name="Range_Train" sheetId="4" r:id="rId4"/>
+    <sheet name="Stage" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,6 +96,66 @@
   </si>
   <si>
     <t>Simple Normal Monster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 기차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 기차는 모든 기차에 기본이 되는 기차이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기관총 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠른 속도로 적을 공격 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사일 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염으로 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들을 느리게 하고 지속 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -557,13 +619,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F71F09-AAA2-4153-8911-01F6B84D29A3}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="12" width="15.640625" customWidth="1"/>
+    <col min="1" max="2" width="15.640625" customWidth="1"/>
+    <col min="3" max="3" width="46.28515625" customWidth="1"/>
+    <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -576,29 +640,140 @@
       <c r="D1" t="s">
         <v>4</v>
       </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>20001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A69F95F5-BFD8-4802-BEEF-4E64ACA1D2AD}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="2" width="15.640625" customWidth="1"/>
+    <col min="3" max="3" width="47.92578125" customWidth="1"/>
+    <col min="4" max="13" width="15.640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
       <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>30001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>30002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>30003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -607,7 +782,101 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C0E03ED-3AF7-4709-A747-0BBF8E83F969}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="2" width="15.640625" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" customWidth="1"/>
+    <col min="4" max="13" width="15.640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>40001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>40002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8290FC1E-2FDC-4D71-B553-D3481951DBAD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32128F88-0986-4A39-BCC5-5A863A5F8FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB9411D-1E8A-4BCD-9D70-E9ADFCD63F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{2E752C8B-AE93-4C4A-8F61-A51C643EC55B}"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E752C8B-AE93-4C4A-8F61-A51C643EC55B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Monster" sheetId="1" r:id="rId1"/>
-    <sheet name="Train" sheetId="2" r:id="rId2"/>
-    <sheet name="Turret_Train" sheetId="5" r:id="rId3"/>
-    <sheet name="Range_Train" sheetId="4" r:id="rId4"/>
-    <sheet name="Stage" sheetId="3" r:id="rId5"/>
+    <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Train_Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Turret_Train_Data" sheetId="5" r:id="rId3"/>
+    <sheet name="Range_Train_Data" sheetId="4" r:id="rId4"/>
+    <sheet name="Stage_Data" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB9411D-1E8A-4BCD-9D70-E9ADFCD63F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2E752C8B-AE93-4C4A-8F61-A51C643EC55B}"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -21,11 +15,11 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -33,136 +27,176 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>move_speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_delay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_exp_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_exp_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_money_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_money_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal Monster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Simple Normal Monster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_interval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 기차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 기차는 모든 기차에 기본이 되는 기차이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기관총 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>빠른 속도로 적을 공격 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미사일 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염으로 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉기 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충격 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들을 느리게 하고 지속 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="42">
+  <si>
+    <t xml:space="preserve">id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal Monster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple Normal Monster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차는 모든 기차에 기본이 되는 기차이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">빠른 속도로 적을 공격 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 느리게 하고 지속 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slime_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">range_basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turret_basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turret</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -213,11 +247,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -519,9 +553,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3471E24B-AE0D-4DFF-834F-29B628C5133E}">
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
@@ -534,79 +568,79 @@
     <col min="12" max="12" width="11.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A2" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="0">
+        <v>20</v>
+      </c>
+      <c r="E2" s="0">
+        <v>2</v>
+      </c>
+      <c r="F2" s="0">
+        <v>6</v>
+      </c>
+      <c r="G2" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H2" s="0">
+        <v>10</v>
+      </c>
+      <c r="I2" s="0">
+        <v>15</v>
+      </c>
+      <c r="J2" s="0">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="K2" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>10001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
-        <v>20</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>15</v>
-      </c>
-      <c r="J2">
-        <v>5</v>
-      </c>
-      <c r="K2">
-        <v>7</v>
-      </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <v>5</v>
       </c>
     </row>
@@ -618,41 +652,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F71F09-AAA2-4153-8911-01F6B84D29A3}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>20001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2">
-        <v>100</v>
+      <c r="D1" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55">
+      <c r="A2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="0" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -663,116 +697,116 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A69F95F5-BFD8-4802-BEEF-4E64ACA1D2AD}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="47.92578125" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55">
+      <c r="A2" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0">
+        <v>3</v>
+      </c>
+      <c r="G2" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>30001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2">
+      <c r="H2" s="0">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
+        <v>30002</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="0">
         <v>100</v>
       </c>
-      <c r="E2">
+      <c r="E3" s="0">
         <v>5</v>
       </c>
-      <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="G2">
+      <c r="F3" s="0">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>30002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3">
+      <c r="G3" s="0">
+        <v>1</v>
+      </c>
+      <c r="H3" s="0">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
+        <v>30003</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="0">
         <v>100</v>
       </c>
-      <c r="E3">
+      <c r="E4" s="0">
+        <v>10</v>
+      </c>
+      <c r="F4" s="0">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="G4" s="0">
         <v>1</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>30003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>1</v>
       </c>
     </row>
@@ -783,90 +817,90 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C0E03ED-3AF7-4709-A747-0BBF8E83F969}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="47.28515625" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55">
+      <c r="A2" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0">
+        <v>5</v>
+      </c>
+      <c r="F2" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>40001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2">
+      <c r="G2" s="0">
+        <v>1</v>
+      </c>
+      <c r="H2" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
+        <v>40002</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="0">
         <v>100</v>
       </c>
-      <c r="E2">
+      <c r="E3" s="0">
         <v>5</v>
       </c>
-      <c r="F2">
+      <c r="F3" s="0">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="G3" s="0">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>40002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>5</v>
       </c>
     </row>
@@ -877,9 +911,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8290FC1E-2FDC-4D71-B553-D3481951DBAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -35,16 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="38">
   <si>
     <t xml:space="preserve">id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">description</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -85,14 +81,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Normal Monster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple Normal Monster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">attack_damage</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -105,22 +93,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">메인 기차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차는 모든 기차에 기본이 되는 기차이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">빠른 속도로 적을 공격 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">미사일 포탑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -137,18 +109,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">냉기 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">충격 포탑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 느리게 하고 지속 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -190,6 +154,21 @@
   </si>
   <si>
     <t xml:space="preserve">Turret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5</t>
   </si>
 </sst>
 </file>
@@ -573,75 +552,75 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="F1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="0" t="s">
+      <c r="G1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="H1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="I1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="J1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="K1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="L1" s="0" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="0" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A2" s="0" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="0">
-        <v>20</v>
-      </c>
-      <c r="E2" s="0">
-        <v>2</v>
-      </c>
-      <c r="F2" s="0">
-        <v>6</v>
-      </c>
-      <c r="G2" s="0">
-        <v>1</v>
-      </c>
-      <c r="H2" s="0">
-        <v>10</v>
-      </c>
-      <c r="I2" s="0">
-        <v>15</v>
-      </c>
-      <c r="J2" s="0">
-        <v>5</v>
-      </c>
-      <c r="K2" s="0">
-        <v>7</v>
-      </c>
-      <c r="L2" s="0">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -653,7 +632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -661,31 +640,37 @@
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="0" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="0" t="b">
+        <v>28</v>
+      </c>
+      <c r="D2" s="0">
+        <v>100</v>
+      </c>
+      <c r="E2" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -698,7 +683,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -706,107 +691,119 @@
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A2" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="0">
+        <v>100</v>
+      </c>
+      <c r="E2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0">
+        <v>5</v>
+      </c>
+      <c r="G2" s="0">
+        <v>10</v>
+      </c>
+      <c r="H2" s="0">
+        <v>1</v>
+      </c>
+      <c r="I2" s="0">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0">
-        <v>5</v>
-      </c>
-      <c r="F2" s="0">
-        <v>3</v>
-      </c>
-      <c r="G2" s="0">
-        <v>1</v>
-      </c>
-      <c r="H2" s="0">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="0">
         <v>30002</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D3" s="0">
         <v>100</v>
       </c>
       <c r="E3" s="0">
+        <v>100</v>
+      </c>
+      <c r="F3" s="0">
         <v>5</v>
       </c>
-      <c r="F3" s="0">
-        <v>1</v>
-      </c>
       <c r="G3" s="0">
         <v>1</v>
       </c>
       <c r="H3" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" s="0">
         <v>0.2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="0">
         <v>30003</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D4" s="0">
         <v>100</v>
       </c>
       <c r="E4" s="0">
+        <v>100</v>
+      </c>
+      <c r="F4" s="0">
         <v>10</v>
       </c>
-      <c r="F4" s="0">
+      <c r="G4" s="0">
         <v>5</v>
       </c>
-      <c r="G4" s="0">
-        <v>1</v>
-      </c>
       <c r="H4" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" s="0">
         <v>1</v>
       </c>
     </row>
@@ -818,7 +815,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -826,81 +823,90 @@
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A2" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="0">
+        <v>100</v>
+      </c>
+      <c r="E2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0">
+        <v>5</v>
+      </c>
+      <c r="G2" s="0">
+        <v>10</v>
+      </c>
+      <c r="H2" s="0">
+        <v>1</v>
+      </c>
+      <c r="I2" s="0">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0">
-        <v>5</v>
-      </c>
-      <c r="F2" s="0">
-        <v>1</v>
-      </c>
-      <c r="G2" s="0">
-        <v>1</v>
-      </c>
-      <c r="H2" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="0">
         <v>40002</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D3" s="0">
         <v>100</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0">
         <v>5</v>
       </c>
-      <c r="F3" s="0">
-        <v>1</v>
-      </c>
       <c r="G3" s="0">
         <v>1</v>
       </c>
       <c r="H3" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" s="0">
         <v>5</v>
       </c>
     </row>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3"/>
+    <workbookView xWindow="7680" yWindow="-15555" windowWidth="16605" windowHeight="10845" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
   <si>
     <t xml:space="preserve">id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,55 +120,53 @@
     <t xml:space="preserve">monster_name</t>
   </si>
   <si>
-    <t xml:space="preserve">slime_01</t>
+    <t xml:space="preserve">basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Slime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">10;20;30</t>
   </si>
   <si>
     <t xml:space="preserve">train_basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">range_basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turret_basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turret</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
   </si>
 </sst>
 </file>
@@ -586,41 +584,41 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="0">
+        <v>10001</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>23</v>
-      </c>
       <c r="D2" s="0" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -645,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -654,18 +652,18 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="0" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D2" s="0">
         <v>100</v>
@@ -683,7 +681,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -696,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -705,7 +703,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>10</v>
@@ -721,32 +719,32 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
-        <v>31</v>
+      <c r="A2" s="0">
+        <v>30001</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2" s="0" t="b">
-        <v>0</v>
+      <c r="E2" s="0">
+        <v>100</v>
       </c>
       <c r="F2" s="0">
         <v>5</v>
       </c>
       <c r="G2" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H2" s="0">
         <v>1</v>
       </c>
       <c r="I2" s="0">
-        <v>2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55">
@@ -754,10 +752,10 @@
         <v>30002</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="0">
         <v>100</v>
@@ -766,44 +764,15 @@
         <v>100</v>
       </c>
       <c r="F3" s="0">
+        <v>10</v>
+      </c>
+      <c r="G3" s="0">
         <v>5</v>
       </c>
-      <c r="G3" s="0">
-        <v>1</v>
-      </c>
       <c r="H3" s="0">
         <v>1</v>
       </c>
       <c r="I3" s="0">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A4" s="0">
-        <v>30003</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="0">
-        <v>100</v>
-      </c>
-      <c r="E4" s="0">
-        <v>100</v>
-      </c>
-      <c r="F4" s="0">
-        <v>10</v>
-      </c>
-      <c r="G4" s="0">
-        <v>5</v>
-      </c>
-      <c r="H4" s="0">
-        <v>1</v>
-      </c>
-      <c r="I4" s="0">
         <v>1</v>
       </c>
     </row>
@@ -815,7 +784,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -828,7 +797,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -837,7 +806,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>10</v>
@@ -853,14 +822,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
-        <v>29</v>
+      <c r="A2" s="0">
+        <v>40001</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D2" s="0">
         <v>100</v>
@@ -872,41 +841,12 @@
         <v>5</v>
       </c>
       <c r="G2" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H2" s="0">
         <v>1</v>
       </c>
       <c r="I2" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
-        <v>40002</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="0">
-        <v>100</v>
-      </c>
-      <c r="E3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0">
-        <v>5</v>
-      </c>
-      <c r="G3" s="0">
-        <v>1</v>
-      </c>
-      <c r="H3" s="0">
-        <v>1</v>
-      </c>
-      <c r="I3" s="0">
         <v>5</v>
       </c>
     </row>
@@ -918,10 +858,38 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
+        <v>50001</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="0">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -3,8 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318DB933-A1C0-4B0E-86AF-ED5CD8D3B037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7680" yWindow="-15555" windowWidth="16605" windowHeight="10845" activeTab="4"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -12,14 +18,16 @@
     <sheet name="Turret_Train_Data" sheetId="5" r:id="rId3"/>
     <sheet name="Range_Train_Data" sheetId="4" r:id="rId4"/>
     <sheet name="Stage_Data" sheetId="3" r:id="rId5"/>
+    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId6"/>
+    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -27,153 +35,176 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
-  <si>
-    <t xml:space="preserve">id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Slime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">10;20;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_basic</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>move_speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_exp_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_exp_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_money_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_money_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사일 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염으로 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster_name</t>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>train_name</t>
+  </si>
+  <si>
+    <t>is_main_train</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>stage_inspection_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage_end_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10;20;30</t>
+  </si>
+  <si>
+    <t>train_basic</t>
+  </si>
+  <si>
+    <t>weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choice_Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>train_Data_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_data_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_Data_Weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target_Train_Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -224,11 +255,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -530,9 +561,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
@@ -545,79 +576,79 @@
     <col min="12" max="12" width="11.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>10001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -629,46 +660,46 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="0" t="b">
+      <c r="E2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -680,99 +711,99 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="47.92578125" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>30001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2">
         <v>100</v>
       </c>
-      <c r="F2" s="0">
+      <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2" s="0">
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>0.2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>30002</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3">
         <v>100</v>
       </c>
-      <c r="F3" s="0">
+      <c r="F3">
         <v>10</v>
       </c>
-      <c r="G3" s="0">
+      <c r="G3">
         <v>5</v>
       </c>
-      <c r="H3" s="0">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3" s="0">
+      <c r="I3">
         <v>1</v>
       </c>
     </row>
@@ -783,70 +814,70 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="47.28515625" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>40001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="0" t="b">
+      <c r="E2" t="b">
         <v>0</v>
       </c>
-      <c r="F2" s="0">
+      <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2" s="0">
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>5</v>
       </c>
     </row>
@@ -857,33 +888,33 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="21.140625" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>50001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>180</v>
       </c>
     </row>
@@ -892,4 +923,79 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFA9861-11E4-4B91-BB73-9FE61424E6A0}">
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="16.92578125" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="13.92578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944099CA-CBCA-415A-AFA2-2DF61D5E4CE1}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.78515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{318DB933-A1C0-4B0E-86AF-ED5CD8D3B037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076EC1A3-35C1-4121-9B06-17994D13ABB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,9 @@
     <sheet name="Stage_Data" sheetId="3" r:id="rId5"/>
     <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId6"/>
     <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId7"/>
+    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId8"/>
+    <sheet name="Turret_Train_UpgradeData" sheetId="9" r:id="rId9"/>
+    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,9 +140,6 @@
     <t>is_main_train</t>
   </si>
   <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -159,10 +159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Basic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Slime</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -174,30 +170,45 @@
     <t>10;20;30</t>
   </si>
   <si>
-    <t>train_basic</t>
-  </si>
-  <si>
     <t>weight</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>choice_Type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>train_Data_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upgrade_data_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upgrade_Data_Weight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>target_Train_Id</t>
+    <t>train_data_id</t>
+  </si>
+  <si>
+    <t>target_train_id</t>
+  </si>
+  <si>
+    <t>기관총 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기관총으로 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인기차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제일 기본이 되는 기차이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weighted_upgrade_ids</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -619,43 +630,103 @@
         <v>10001</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
       <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
         <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BD03D1-5D02-4A2E-97F6-4C786BABBB78}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="8" width="15.640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>100001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>100002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>100003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>100004</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -687,20 +758,20 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>35</v>
+      <c r="A2">
+        <v>20001</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D2">
         <v>100</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -712,7 +783,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -754,28 +825,28 @@
         <v>30001</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2">
-        <v>100</v>
+      <c r="E2" t="b">
+        <v>0</v>
       </c>
       <c r="F2">
         <v>5</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
@@ -783,43 +854,73 @@
         <v>30002</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>30003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="F3">
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>10</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>5</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="50.28515625" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -879,6 +980,35 @@
       </c>
       <c r="I2">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>40002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3">
+        <v>100</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -901,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -912,7 +1042,7 @@
         <v>50001</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2">
         <v>180</v>
@@ -926,38 +1056,82 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFFA9861-11E4-4B91-BB73-9FE61424E6A0}">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12.640625" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
     <col min="5" max="5" width="16.92578125" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="13.92578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" t="s">
-        <v>41</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>60001</v>
+      </c>
+      <c r="B2">
+        <v>30001</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>60002</v>
+      </c>
+      <c r="B3">
+        <v>30002</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>60003</v>
+      </c>
+      <c r="B4">
+        <v>30003</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>60004</v>
+      </c>
+      <c r="B5">
+        <v>40001</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>60005</v>
+      </c>
+      <c r="B6">
+        <v>40002</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -968,12 +1142,13 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{944099CA-CBCA-415A-AFA2-2DF61D5E4CE1}">
-  <dimension ref="A1:E1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.92578125" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
     <col min="5" max="5" width="13.78515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -982,16 +1157,184 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>70001</v>
+      </c>
+      <c r="B2">
+        <v>30001</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>70002</v>
+      </c>
+      <c r="B3">
+        <v>30002</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>70003</v>
+      </c>
+      <c r="B4">
+        <v>30003</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>70004</v>
+      </c>
+      <c r="B5">
+        <v>40001</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>70005</v>
+      </c>
+      <c r="B6">
+        <v>40002</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84517C9E-E38E-4A09-A50B-E00504ACBE9C}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>80001</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E50DA9-A70A-4558-8529-6E6BDC7C52F5}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>90001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>90002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>90003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>90004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>90005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>90006</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076EC1A3-35C1-4121-9B06-17994D13ABB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A38C90-1706-4A66-8F1E-B0F70AEF9FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,9 @@
     <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId6"/>
     <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId7"/>
     <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId8"/>
-    <sheet name="Turret_Train_UpgradeData" sheetId="9" r:id="rId9"/>
+    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId9"/>
     <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
+    <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="76">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -128,87 +129,209 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>is_main_train</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>stage_inspection_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage_end_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10;20;30</t>
+  </si>
+  <si>
+    <t>weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>train_data_id</t>
+  </si>
+  <si>
+    <t>target_train_id</t>
+  </si>
+  <si>
+    <t>기관총 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기관총으로 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제일 기본이 되는 기차이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0} 증가 공격딜레이 {1} 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0} 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0} 증가 범위 {1} 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭발 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0} 증가 범위 {2} 증가</t>
+  </si>
+  <si>
+    <t>need_money</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_upgrade_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 딜레이 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득하는 골드 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득하는 경험치 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포탑들의 공격 딜레이가 {0}만큼 감소합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포탑들의 체력이 {0}만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포탑들의 공격력이 {0}만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 처치 시 획득하는 골드가 {0}만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 처치 시 획득하는 경험치가 {0}만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>monster_name</t>
   </si>
   <si>
-    <t>basic</t>
-  </si>
-  <si>
     <t>train_name</t>
   </si>
   <si>
-    <t>is_main_train</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>stage_inspection_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stage_end_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10;20;30</t>
-  </si>
-  <si>
-    <t>weight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>train_data_id</t>
-  </si>
-  <si>
-    <t>target_train_id</t>
-  </si>
-  <si>
-    <t>기관총 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기관총으로 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인기차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제일 기본이 되는 기차이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉기 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>weighted_upgrade_ids</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>upgrade_name</t>
+  </si>
+  <si>
+    <t>weighted_upgrades</t>
+  </si>
+  <si>
+    <t>prefab_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>projectile_prefab_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalTurretTrain</t>
+  </si>
+  <si>
+    <t>FireTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissileTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalTurretProjectile</t>
+  </si>
+  <si>
+    <t>FireEffectProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissileProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExplosionTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColdAirTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExplosionProjectile</t>
+  </si>
+  <si>
+    <t>ColdAirProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_id</t>
+  </si>
+  <si>
+    <t>MainTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 기차</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -573,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
@@ -585,14 +708,15 @@
     <col min="10" max="10" width="15.35546875" customWidth="1"/>
     <col min="11" max="11" width="15.92578125" customWidth="1"/>
     <col min="12" max="12" width="11.78515625" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -624,43 +748,49 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>10001</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
+      <c r="M2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -671,19 +801,21 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BD03D1-5D02-4A2E-97F6-4C786BABBB78}">
-  <dimension ref="A1:H5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="8" width="15.640625" customWidth="1"/>
+    <col min="2" max="2" width="15.640625" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="8" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -692,36 +824,53 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>100001</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>100002</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>100003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>100004</v>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -730,9 +879,151 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.92578125" customWidth="1"/>
+    <col min="4" max="4" width="12.92578125" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" customWidth="1"/>
+    <col min="6" max="6" width="18.78515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>110001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>110002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3">
+        <v>200</v>
+      </c>
+      <c r="E3">
+        <v>0.1</v>
+      </c>
+      <c r="F3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>110003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>110004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5">
+        <v>300</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>110005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6">
+        <v>500</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -740,12 +1031,12 @@
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -754,24 +1045,33 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>20001</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D2">
         <v>100</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -783,20 +1083,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="47.92578125" customWidth="1"/>
-    <col min="4" max="13" width="15.640625" customWidth="1"/>
+    <col min="4" max="5" width="15.640625" customWidth="1"/>
+    <col min="6" max="6" width="18.92578125" customWidth="1"/>
+    <col min="7" max="10" width="15.640625" customWidth="1"/>
+    <col min="11" max="11" width="20.92578125" customWidth="1"/>
+    <col min="12" max="12" width="19.28515625" customWidth="1"/>
+    <col min="13" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -805,30 +1110,39 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="L1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>30001</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -836,20 +1150,26 @@
       <c r="E2" t="b">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="L2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>30002</v>
       </c>
@@ -865,20 +1185,26 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H3">
         <v>5</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
       <c r="I3">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>0.1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>30003</v>
       </c>
@@ -894,17 +1220,23 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4">
         <v>10</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>5</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -916,20 +1248,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" customWidth="1"/>
-    <col min="4" max="13" width="15.640625" customWidth="1"/>
+    <col min="4" max="10" width="15.640625" customWidth="1"/>
+    <col min="11" max="11" width="18.2109375" customWidth="1"/>
+    <col min="12" max="12" width="21" customWidth="1"/>
+    <col min="13" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -938,22 +1273,31 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="L1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>40001</v>
       </c>
@@ -969,28 +1313,34 @@
       <c r="E2" t="b">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2">
         <v>5</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
       </c>
       <c r="I2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>40002</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -998,17 +1348,23 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3">
         <v>5</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
       <c r="I3">
         <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1031,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1042,7 +1398,7 @@
         <v>50001</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>180</v>
@@ -1073,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1157,16 +1513,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1176,6 +1532,9 @@
       <c r="B2">
         <v>30001</v>
       </c>
+      <c r="C2">
+        <v>90001</v>
+      </c>
       <c r="D2">
         <v>0</v>
       </c>
@@ -1190,6 +1549,9 @@
       <c r="B3">
         <v>30002</v>
       </c>
+      <c r="C3">
+        <v>90002</v>
+      </c>
       <c r="D3">
         <v>0</v>
       </c>
@@ -1204,6 +1566,9 @@
       <c r="B4">
         <v>30003</v>
       </c>
+      <c r="C4">
+        <v>90003</v>
+      </c>
       <c r="D4">
         <v>0</v>
       </c>
@@ -1218,6 +1583,9 @@
       <c r="B5">
         <v>40001</v>
       </c>
+      <c r="C5">
+        <v>100001</v>
+      </c>
       <c r="D5">
         <v>0</v>
       </c>
@@ -1231,6 +1599,9 @@
       </c>
       <c r="B6">
         <v>40002</v>
+      </c>
+      <c r="C6">
+        <v>100002</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1246,16 +1617,32 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84517C9E-E38E-4A09-A50B-E00504ACBE9C}">
-  <dimension ref="A1:A2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="15.78515625" customWidth="1"/>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>80001</v>
       </c>
@@ -1268,12 +1655,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E50DA9-A70A-4558-8529-6E6BDC7C52F5}">
-  <dimension ref="A1:H7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
@@ -1281,12 +1668,12 @@
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1295,50 +1682,72 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>90001</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>90002</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>90003</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>90004</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>90005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>90006</v>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A38C90-1706-4A66-8F1E-B0F70AEF9FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61116910-F4F6-4301-ACE9-0D554AE98508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="16500" yWindow="-14460" windowWidth="16605" windowHeight="10845" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,9 +144,6 @@
     <t>20</t>
   </si>
   <si>
-    <t>1.5</t>
-  </si>
-  <si>
     <t>stage_inspection_time</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -332,6 +329,18 @@
   </si>
   <si>
     <t>메인 기차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이저 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이저로 강하게 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LaserTurretTrain</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -716,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -749,7 +758,7 @@
         <v>10</v>
       </c>
       <c r="M1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -757,7 +766,7 @@
         <v>10001</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -765,8 +774,8 @@
       <c r="D2">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
+      <c r="E2">
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -786,11 +795,11 @@
       <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
-        <v>25</v>
+      <c r="L2">
+        <v>1.5</v>
       </c>
       <c r="M2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -815,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -824,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
         <v>10</v>
@@ -844,10 +853,10 @@
         <v>100001</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -861,10 +870,10 @@
         <v>100002</v>
       </c>
       <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
         <v>41</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -896,22 +905,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
-        <v>45</v>
-      </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -919,10 +928,10 @@
         <v>110001</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -939,10 +948,10 @@
         <v>110002</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D3">
         <v>200</v>
@@ -959,10 +968,10 @@
         <v>110003</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4">
         <v>50</v>
@@ -979,10 +988,10 @@
         <v>110004</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>300</v>
@@ -999,10 +1008,10 @@
         <v>110005</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>500</v>
@@ -1036,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1048,10 +1057,10 @@
         <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
@@ -1059,10 +1068,10 @@
         <v>20001</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -1071,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -1101,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1113,10 +1122,10 @@
         <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H1" t="s">
         <v>10</v>
@@ -1131,7 +1140,7 @@
         <v>5</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1139,10 +1148,10 @@
         <v>30001</v>
       </c>
       <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>34</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -1151,7 +1160,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -1166,7 +1175,7 @@
         <v>0.3</v>
       </c>
       <c r="L2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1186,7 +1195,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -1201,7 +1210,7 @@
         <v>0.1</v>
       </c>
       <c r="L3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1221,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -1236,7 +1245,27 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>30004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1264,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1276,10 +1305,10 @@
         <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H1" t="s">
         <v>10</v>
@@ -1294,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1314,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -1329,7 +1358,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -1337,10 +1366,10 @@
         <v>40002</v>
       </c>
       <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -1349,7 +1378,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -1364,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1387,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1398,7 +1427,7 @@
         <v>50001</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>180</v>
@@ -1429,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -1513,16 +1542,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1630,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1639,7 +1668,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -1673,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1682,7 +1711,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
         <v>10</v>
@@ -1702,10 +1731,10 @@
         <v>90001</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1722,7 +1751,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1736,7 +1765,7 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4">
         <v>1</v>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61116910-F4F6-4301-ACE9-0D554AE98508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="16500" yWindow="-14460" windowWidth="16605" windowHeight="10845" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -27,11 +21,11 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -39,308 +33,312 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>move_speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_delay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_exp_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_exp_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_money_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_money_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_interval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미사일 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염으로 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충격 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>basic</t>
-  </si>
-  <si>
-    <t>is_main_train</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>stage_inspection_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stage_end_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10;20;30</t>
-  </si>
-  <si>
-    <t>weight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>train_data_id</t>
-  </si>
-  <si>
-    <t>target_train_id</t>
-  </si>
-  <si>
-    <t>기관총 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기관총으로 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제일 기본이 되는 기차이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉기 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 {0} 증가 공격딜레이 {1} 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 {0} 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 {0} 증가 범위 {1} 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>폭발 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 {0} 증가 범위 {2} 증가</t>
-  </si>
-  <si>
-    <t>need_money</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upgrade_value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_upgrade_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 딜레이 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>획득하는 골드 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>획득하는 경험치 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포탑들의 공격 딜레이가 {0}만큼 감소합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포탑들의 체력이 {0}만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포탑들의 공격력이 {0}만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 처치 시 획득하는 골드가 {0}만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 처치 시 획득하는 경험치가 {0}만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>monster_name</t>
-  </si>
-  <si>
-    <t>train_name</t>
-  </si>
-  <si>
-    <t>upgrade_name</t>
-  </si>
-  <si>
-    <t>weighted_upgrades</t>
-  </si>
-  <si>
-    <t>prefab_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>projectile_prefab_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseMonster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NormalTurretTrain</t>
-  </si>
-  <si>
-    <t>FireTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissileTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NormalTurretProjectile</t>
-  </si>
-  <si>
-    <t>FireEffectProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissileProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExplosionTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColdAirTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExplosionProjectile</t>
-  </si>
-  <si>
-    <t>ColdAirProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_id</t>
-  </si>
-  <si>
-    <t>MainTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 기차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이저 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이저로 강하게 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LaserTurretTrain</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="79">
+  <si>
+    <t xml:space="preserve">id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">10;20;30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {2} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}만큼 감소합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -348,6 +346,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -398,11 +397,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -704,9 +703,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
@@ -720,85 +719,85 @@
     <col min="13" max="13" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="0" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>10001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <v>1.5</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="0" t="s">
         <v>61</v>
       </c>
     </row>
@@ -810,75 +809,75 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="27.5" customWidth="1"/>
     <col min="4" max="8" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>100001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>2</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+      <c r="F2" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>100002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="0">
+        <v>1</v>
+      </c>
+      <c r="F3" s="0">
         <v>1</v>
       </c>
     </row>
@@ -889,9 +888,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="43.92578125" customWidth="1"/>
@@ -900,126 +899,126 @@
     <col min="6" max="6" width="18.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>110001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="0">
+        <v>1</v>
+      </c>
+      <c r="F2" s="0">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>110002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>200</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>0.1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>110003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>50</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="0">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A5" s="0">
         <v>110004</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>300</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <v>10</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A6" s="0">
         <v>110005</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <v>500</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <v>10</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>10</v>
       </c>
     </row>
@@ -1031,55 +1030,55 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>20001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1091,9 +1090,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="47.92578125" customWidth="1"/>
@@ -1105,167 +1104,182 @@
     <col min="13" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>30001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>5</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>3</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="J2" s="0">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0">
         <v>0.3</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="0" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>30002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>100</v>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>5</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
+      <c r="I3" s="0">
+        <v>1</v>
+      </c>
+      <c r="J3" s="0">
+        <v>1</v>
+      </c>
+      <c r="K3" s="0">
         <v>0.1</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="0" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>30003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>100</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>10</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="0">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="J4" s="0">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0">
+        <v>1</v>
+      </c>
+      <c r="L4" s="0" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A5" s="0">
         <v>30004</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>100</v>
       </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="s">
         <v>77</v>
+      </c>
+      <c r="H5" s="0">
+        <v>15</v>
+      </c>
+      <c r="I5" s="0">
+        <v>30</v>
+      </c>
+      <c r="J5" s="0">
+        <v>1</v>
+      </c>
+      <c r="K5" s="0">
+        <v>5</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1276,9 +1290,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" customWidth="1"/>
@@ -1288,111 +1302,111 @@
     <col min="13" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>40001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>5</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>5</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="J2" s="0">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="0" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>40002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>100</v>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>5</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="I3" s="0">
+        <v>1</v>
+      </c>
+      <c r="J3" s="0">
+        <v>1</v>
+      </c>
+      <c r="K3" s="0">
+        <v>1</v>
+      </c>
+      <c r="L3" s="0" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1403,33 +1417,33 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.140625" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>50001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>180</v>
       </c>
     </row>
@@ -1441,9 +1455,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12.640625" customWidth="1"/>
@@ -1453,69 +1467,80 @@
     <col min="7" max="7" width="13.92578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>60001</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>30001</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>60002</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>30002</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="C3" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>60003</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>30003</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
+      <c r="C4" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A5" s="0">
         <v>60004</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
+        <v>30004</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A6" s="0">
+        <v>60005</v>
+      </c>
+      <c r="B6" s="0">
         <v>40001</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>60005</v>
-      </c>
-      <c r="B6">
+      <c r="C6" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A7" s="0">
+        <v>60006</v>
+      </c>
+      <c r="B7" s="0">
         <v>40002</v>
       </c>
-      <c r="C6">
+      <c r="C7" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1527,9 +1552,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="13.92578125" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" customWidth="1"/>
@@ -1537,105 +1562,105 @@
     <col min="5" max="5" width="13.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>70001</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>30001</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>90001</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="0">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>70002</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>30002</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>90002</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="D3" s="0">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>70003</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>30003</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>90003</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
+      <c r="D4" s="0">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A5" s="0">
         <v>70004</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>40001</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>100001</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
+      <c r="D5" s="0">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A6" s="0">
         <v>70005</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>40002</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>100002</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="0">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1646,33 +1671,33 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.78515625" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>80001</v>
       </c>
     </row>
@@ -1684,9 +1709,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" customWidth="1"/>
@@ -1697,80 +1722,80 @@
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>90001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="H2">
+      <c r="F2" s="0">
+        <v>1</v>
+      </c>
+      <c r="H2" s="0">
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>90002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="F3" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>90003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="H4">
+      <c r="F4" s="0">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0">
         <v>0.1</v>
       </c>
     </row>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -1486,7 +1486,7 @@
         <v>30001</v>
       </c>
       <c r="C2" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55">
@@ -1519,7 +1519,7 @@
         <v>30004</v>
       </c>
       <c r="C5" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.55">

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" activeTab="5"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -234,26 +234,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}만큼 감소합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">monster_name</t>
   </si>
   <si>
@@ -339,6 +319,26 @@
   </si>
   <si>
     <t xml:space="preserve">LaserProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -757,7 +757,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55">
@@ -798,7 +798,7 @@
         <v>1.5</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -816,6 +816,7 @@
     <col min="2" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="27.5" customWidth="1"/>
     <col min="4" max="8" width="15.640625" customWidth="1"/>
+    <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
@@ -823,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -832,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>10</v>
@@ -857,10 +858,10 @@
       <c r="C2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="0">
+      <c r="F2" s="0">
         <v>2</v>
       </c>
-      <c r="F2" s="0">
+      <c r="G2" s="0">
         <v>1</v>
       </c>
     </row>
@@ -874,10 +875,10 @@
       <c r="C3" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="0">
-        <v>1</v>
-      </c>
       <c r="F3" s="0">
+        <v>1</v>
+      </c>
+      <c r="G3" s="0">
         <v>1</v>
       </c>
     </row>
@@ -893,10 +894,11 @@
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="43.92578125" customWidth="1"/>
+    <col min="3" max="3" width="48.5703125" customWidth="1"/>
     <col min="4" max="4" width="12.92578125" customWidth="1"/>
     <col min="5" max="5" width="15.140625" customWidth="1"/>
     <col min="6" max="6" width="18.78515625" customWidth="1"/>
+    <col min="7" max="7" width="12.78515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55">
@@ -904,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -919,7 +921,7 @@
         <v>44</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55">
@@ -930,7 +932,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="D2" s="0">
         <v>100</v>
@@ -950,13 +952,13 @@
         <v>46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D3" s="0">
         <v>200</v>
       </c>
       <c r="E3" s="0">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" s="0">
         <v>100</v>
@@ -970,7 +972,7 @@
         <v>47</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="D4" s="0">
         <v>50</v>
@@ -990,7 +992,7 @@
         <v>48</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="D5" s="0">
         <v>300</v>
@@ -1010,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D6" s="0">
         <v>500</v>
@@ -1044,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -1056,10 +1058,10 @@
         <v>21</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55">
@@ -1067,7 +1069,7 @@
         <v>20001</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
@@ -1079,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1109,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -1121,10 +1123,10 @@
         <v>21</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H1" s="0" t="s">
         <v>10</v>
@@ -1139,7 +1141,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55">
@@ -1159,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H2" s="0">
         <v>5</v>
@@ -1174,7 +1176,7 @@
         <v>0.3</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55">
@@ -1194,7 +1196,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
@@ -1209,7 +1211,7 @@
         <v>0.1</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.55">
@@ -1229,7 +1231,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H4" s="0">
         <v>10</v>
@@ -1244,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="0" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.55">
@@ -1252,10 +1254,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D5" s="0">
         <v>100</v>
@@ -1264,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H5" s="0">
         <v>15</v>
@@ -1279,7 +1281,7 @@
         <v>5</v>
       </c>
       <c r="L5" s="0" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1307,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -1319,10 +1321,10 @@
         <v>21</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H1" s="0" t="s">
         <v>10</v>
@@ -1337,7 +1339,7 @@
         <v>13</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55">
@@ -1357,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H2" s="0">
         <v>5</v>
@@ -1372,7 +1374,7 @@
         <v>5</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55">
@@ -1392,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
@@ -1407,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1572,7 @@
         <v>31</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D1" s="0" t="s">
         <v>29</v>
@@ -1684,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -1693,7 +1695,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55">
@@ -1720,6 +1722,7 @@
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
     <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
@@ -1727,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>1</v>
@@ -1736,7 +1739,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>10</v>
@@ -1761,10 +1764,10 @@
       <c r="C2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="0">
-        <v>1</v>
-      </c>
-      <c r="H2" s="0">
+      <c r="G2" s="0">
+        <v>1</v>
+      </c>
+      <c r="I2" s="0">
         <v>0.1</v>
       </c>
     </row>
@@ -1778,7 +1781,7 @@
       <c r="C3" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="0">
+      <c r="G3" s="0">
         <v>1</v>
       </c>
     </row>
@@ -1792,10 +1795,10 @@
       <c r="C4" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="0">
-        <v>1</v>
-      </c>
-      <c r="H4" s="0">
+      <c r="G4" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" s="0">
         <v>0.1</v>
       </c>
     </row>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -3,8 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FBA2C0-4E70-4C1C-9E07-0B4D2A2E2929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="10"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -21,11 +27,11 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -33,312 +39,332 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="79">
-  <si>
-    <t xml:space="preserve">id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">max_hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">move_speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_delay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_exp_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">drop_money_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">attack_interval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">충격 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">basic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is_main_train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_inspection_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Slime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">stage_end_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">10;20;30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">train_data_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">target_train_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">기관총으로 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">냉기 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">폭발 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {2} 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">need_money</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">max_upgrade_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 딜레이 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">체력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 골드 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">획득하는 경험치 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">monster_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">train_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upgrade_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weighted_upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefab_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">projectile_prefab_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">BaseMonster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="84">
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>move_speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_exp_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_exp_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_money_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_money_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사일 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염으로 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>basic</t>
+  </si>
+  <si>
+    <t>is_main_train</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>stage_inspection_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stage_end_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10;20;30</t>
+  </si>
+  <si>
+    <t>weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>train_data_id</t>
+  </si>
+  <si>
+    <t>target_train_id</t>
+  </si>
+  <si>
+    <t>기관총 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기관총으로 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제일 기본이 되는 기차이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0} 증가 공격딜레이 {1} 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0} 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0} 증가 범위 {1} 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭발 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 {0} 증가 범위 {2} 증가</t>
+  </si>
+  <si>
+    <t>need_money</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_upgrade_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 딜레이 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득하는 골드 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득하는 경험치 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monster_name</t>
+  </si>
+  <si>
+    <t>train_name</t>
+  </si>
+  <si>
+    <t>upgrade_name</t>
+  </si>
+  <si>
+    <t>weighted_upgrades</t>
+  </si>
+  <si>
+    <t>prefab_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>projectile_prefab_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalTurretTrain</t>
+  </si>
+  <si>
+    <t>FireTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissileTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalTurretProjectile</t>
+  </si>
+  <si>
+    <t>FireEffectProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MissileProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExplosionTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ColdAirTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExplosionProjectile</t>
+  </si>
+  <si>
+    <t>ColdAirProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_id</t>
+  </si>
+  <si>
+    <t>MainTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 기차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이저 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레이저로 강하게 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LaserTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LaserProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면에 있는 다수의 적들을 전기로 공격한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ElectrickTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ElectrickProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target_count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -346,7 +372,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -397,11 +422,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -703,9 +728,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
@@ -719,85 +744,85 @@
     <col min="13" max="13" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>10001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>10</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2">
         <v>5</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="0">
+      <c r="L2">
         <v>1.5</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" t="s">
         <v>56</v>
       </c>
     </row>
@@ -809,9 +834,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="27.5" customWidth="1"/>
@@ -819,66 +844,66 @@
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>100001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="0">
+      <c r="F2">
         <v>2</v>
       </c>
-      <c r="G2" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>100002</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="0">
-        <v>1</v>
-      </c>
-      <c r="G3" s="0">
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>
@@ -889,9 +914,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" customWidth="1"/>
@@ -901,126 +926,126 @@
     <col min="7" max="7" width="12.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>110001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="0">
-        <v>1</v>
-      </c>
-      <c r="F2" s="0">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>110002</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>200</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3">
         <v>-0.1</v>
       </c>
-      <c r="F3" s="0">
+      <c r="F3">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A4" s="0">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
         <v>110003</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>50</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="F4" s="0">
+      <c r="F4">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A5" s="0">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
         <v>110004</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>300</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5">
         <v>10</v>
       </c>
-      <c r="F5" s="0">
+      <c r="F5">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A6" s="0">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
         <v>110005</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>78</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>500</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6">
         <v>10</v>
       </c>
-      <c r="F6" s="0">
+      <c r="F6">
         <v>10</v>
       </c>
     </row>
@@ -1032,55 +1057,55 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>20001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1092,9 +1117,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="47.92578125" customWidth="1"/>
@@ -1106,182 +1131,235 @@
     <col min="13" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>30001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="J2" s="0">
-        <v>1</v>
-      </c>
-      <c r="K2" s="0">
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>0.3</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>30002</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="0">
+      <c r="H3">
         <v>5</v>
       </c>
-      <c r="I3" s="0">
-        <v>1</v>
-      </c>
-      <c r="J3" s="0">
-        <v>1</v>
-      </c>
-      <c r="K3" s="0">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
         <v>0.1</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A4" s="0">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
         <v>30003</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="s">
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="0">
+      <c r="H4">
         <v>10</v>
       </c>
-      <c r="I4" s="0">
+      <c r="I4">
         <v>5</v>
       </c>
-      <c r="J4" s="0">
-        <v>1</v>
-      </c>
-      <c r="K4" s="0">
-        <v>1</v>
-      </c>
-      <c r="L4" s="0" t="s">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A5" s="0">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
         <v>30004</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="s">
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="0">
+      <c r="H5">
         <v>15</v>
       </c>
-      <c r="I5" s="0">
+      <c r="I5">
         <v>30</v>
       </c>
-      <c r="J5" s="0">
-        <v>1</v>
-      </c>
-      <c r="K5" s="0">
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <v>5</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>30005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>25</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1.5</v>
+      </c>
+      <c r="L6">
+        <v>5</v>
+      </c>
+      <c r="M6" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1292,9 +1370,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" customWidth="1"/>
@@ -1304,111 +1382,111 @@
     <col min="13" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>40001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="0">
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="I2" s="0">
+      <c r="I2">
         <v>5</v>
       </c>
-      <c r="J2" s="0">
-        <v>1</v>
-      </c>
-      <c r="K2" s="0">
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>5</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>40002</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="0">
+      <c r="H3">
         <v>5</v>
       </c>
-      <c r="I3" s="0">
-        <v>1</v>
-      </c>
-      <c r="J3" s="0">
-        <v>1</v>
-      </c>
-      <c r="K3" s="0">
-        <v>1</v>
-      </c>
-      <c r="L3" s="0" t="s">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1419,33 +1497,33 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="21.140625" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>50001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>180</v>
       </c>
     </row>
@@ -1457,9 +1535,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12.640625" customWidth="1"/>
@@ -1469,80 +1547,91 @@
     <col min="7" max="7" width="13.92578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>60001</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>30001</v>
       </c>
-      <c r="C2" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
+      <c r="C2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>60002</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3">
         <v>30002</v>
       </c>
-      <c r="C3" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A4" s="0">
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
         <v>60003</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B4">
         <v>30003</v>
       </c>
-      <c r="C4" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A5" s="0">
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
         <v>60004</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B5">
         <v>30004</v>
       </c>
-      <c r="C5" s="0">
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>60005</v>
+      </c>
+      <c r="B6">
+        <v>30005</v>
+      </c>
+      <c r="C6">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A6" s="0">
-        <v>60005</v>
-      </c>
-      <c r="B6" s="0">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>60006</v>
+      </c>
+      <c r="B7">
         <v>40001</v>
       </c>
-      <c r="C6" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55">
-      <c r="A7" s="0">
-        <v>60006</v>
-      </c>
-      <c r="B7" s="0">
+      <c r="C7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>60007</v>
+      </c>
+      <c r="B8">
         <v>40002</v>
       </c>
-      <c r="C7" s="0">
+      <c r="C8">
         <v>0</v>
       </c>
     </row>
@@ -1554,9 +1643,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="13.92578125" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" customWidth="1"/>
@@ -1564,105 +1653,105 @@
     <col min="5" max="5" width="13.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>70001</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>30001</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>90001</v>
       </c>
-      <c r="D2" s="0">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>70002</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3">
         <v>30002</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>90002</v>
       </c>
-      <c r="D3" s="0">
-        <v>0</v>
-      </c>
-      <c r="E3" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A4" s="0">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
         <v>70003</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B4">
         <v>30003</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4">
         <v>90003</v>
       </c>
-      <c r="D4" s="0">
-        <v>0</v>
-      </c>
-      <c r="E4" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A5" s="0">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
         <v>70004</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B5">
         <v>40001</v>
       </c>
-      <c r="C5" s="0">
+      <c r="C5">
         <v>100001</v>
       </c>
-      <c r="D5" s="0">
-        <v>0</v>
-      </c>
-      <c r="E5" s="0">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A6" s="0">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
         <v>70005</v>
       </c>
-      <c r="B6" s="0">
+      <c r="B6">
         <v>40002</v>
       </c>
-      <c r="C6" s="0">
+      <c r="C6">
         <v>100002</v>
       </c>
-      <c r="D6" s="0">
-        <v>0</v>
-      </c>
-      <c r="E6" s="0">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
     </row>
@@ -1673,33 +1762,33 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.78515625" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>80001</v>
       </c>
     </row>
@@ -1711,9 +1800,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" customWidth="1"/>
@@ -1725,80 +1814,80 @@
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="0" t="s">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A2" s="0">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>90001</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="0">
-        <v>1</v>
-      </c>
-      <c r="I2" s="0">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A3" s="0">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
         <v>90002</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
-      <c r="A4" s="0">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
         <v>90003</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="0">
-        <v>1</v>
-      </c>
-      <c r="I4" s="0">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>0.1</v>
       </c>
     </row>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FBA2C0-4E70-4C1C-9E07-0B4D2A2E2929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08F4930-7406-48C3-8CEC-2EECD7B4B76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="88">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -365,6 +365,22 @@
   </si>
   <si>
     <t>target_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CannonTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CannonProjectile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1118,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -1360,6 +1376,44 @@
       </c>
       <c r="M6" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>30006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>50</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chang\GitHub\TrainDefense\Assets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08F4930-7406-48C3-8CEC-2EECD7B4B76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -27,11 +21,11 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -39,348 +33,348 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="88">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>description</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_hp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>move_speed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_delay</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_exp_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_exp_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_money_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_money_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_interval</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미사일 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화염으로 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충격 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들을 밀치고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>basic</t>
-  </si>
-  <si>
-    <t>is_main_train</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>stage_inspection_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Slime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stage_end_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10;20;30</t>
-  </si>
-  <si>
-    <t>weight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>train_data_id</t>
-  </si>
-  <si>
-    <t>target_train_id</t>
-  </si>
-  <si>
-    <t>기관총 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기관총으로 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제일 기본이 되는 기차이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉기 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 {0} 증가 공격딜레이 {1} 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 {0} 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 {0} 증가 범위 {1} 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>폭발 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 {0} 증가 범위 {2} 증가</t>
-  </si>
-  <si>
-    <t>need_money</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upgrade_value</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_upgrade_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공격 딜레이 감소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>체력 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>획득하는 골드 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>획득하는 경험치 증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>monster_name</t>
-  </si>
-  <si>
-    <t>train_name</t>
-  </si>
-  <si>
-    <t>upgrade_name</t>
-  </si>
-  <si>
-    <t>weighted_upgrades</t>
-  </si>
-  <si>
-    <t>prefab_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>projectile_prefab_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BaseMonster</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NormalTurretTrain</t>
-  </si>
-  <si>
-    <t>FireTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissileTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NormalTurretProjectile</t>
-  </si>
-  <si>
-    <t>FireEffectProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MissileProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExplosionTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ColdAirTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExplosionProjectile</t>
-  </si>
-  <si>
-    <t>ColdAirProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon_id</t>
-  </si>
-  <si>
-    <t>MainTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 기차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이저 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이저로 강하게 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LaserTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LaserProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전기 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>화면에 있는 다수의 적들을 전기로 공격한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ElectrickTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ElectrickProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>target_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>포격 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CannonTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CannonProjectile</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="88">
+  <si>
+    <t xml:space="preserve">id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">max_hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">move_speed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_exp_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">drop_money_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">attack_interval</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화염으로 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일로 강한 피해를 준다. 공격속도는 느리다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">충격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들을 밀치고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">basic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">is_main_train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_inspection_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Slime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">stage_end_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">10;20;30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">train_data_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">target_train_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총으로 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">제일 기본이 되는 기차이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">범위 내에 있는 적들의 이동속도가 느려지고 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {2} 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">need_money</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">max_upgrade_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 딜레이 감소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">체력 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 골드 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">획득하는 경험치 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">monster_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">train_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weighted_upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefab_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">projectile_prefab_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">BaseMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretTrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalTurretProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -388,6 +382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -438,11 +433,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -744,9 +739,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
@@ -760,85 +755,85 @@
     <col min="13" max="13" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="0" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>10001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="0">
         <v>1.5</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="0" t="s">
         <v>56</v>
       </c>
     </row>
@@ -850,9 +845,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="27.5" customWidth="1"/>
@@ -860,66 +855,66 @@
     <col min="9" max="9" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>100001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>2</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+      <c r="G2" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>100002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="0">
+        <v>1</v>
+      </c>
+      <c r="G3" s="0">
         <v>1</v>
       </c>
     </row>
@@ -930,9 +925,9 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" customWidth="1"/>
@@ -942,126 +937,126 @@
     <col min="7" max="7" width="12.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>110001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="0">
+        <v>1</v>
+      </c>
+      <c r="F2" s="0">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>110002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>200</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>-0.1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>110003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>50</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="0">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="0">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A5" s="0">
         <v>110004</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>48</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>77</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>300</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="0">
         <v>10</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="0">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A6" s="0">
         <v>110005</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <v>500</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="0">
         <v>10</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="0">
         <v>10</v>
       </c>
     </row>
@@ -1073,55 +1068,55 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" customWidth="1"/>
     <col min="4" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>20001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1133,9 +1128,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="47.92578125" customWidth="1"/>
@@ -1147,272 +1142,272 @@
     <col min="13" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>30001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>33</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>5</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>3</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="J2" s="0">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0">
         <v>0.3</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="L2" s="0">
+        <v>0</v>
+      </c>
+      <c r="M2" s="0" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>30002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>100</v>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="s">
         <v>58</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>5</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
+      <c r="I3" s="0">
+        <v>1</v>
+      </c>
+      <c r="J3" s="0">
+        <v>1</v>
+      </c>
+      <c r="K3" s="0">
         <v>0.1</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="L3" s="0">
+        <v>0</v>
+      </c>
+      <c r="M3" s="0" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>30003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0">
         <v>100</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="0">
         <v>10</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="0">
         <v>5</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="J4" s="0">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0">
+        <v>1</v>
+      </c>
+      <c r="L4" s="0">
+        <v>0</v>
+      </c>
+      <c r="M4" s="0" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A5" s="0">
         <v>30004</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0">
         <v>100</v>
       </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="0">
         <v>15</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="0">
         <v>30</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
+      <c r="J5" s="0">
+        <v>1</v>
+      </c>
+      <c r="K5" s="0">
         <v>5</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="L5" s="0">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A6" s="0">
         <v>30005</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0">
         <v>100</v>
       </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="0">
         <v>10</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="0">
         <v>25</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="0">
         <v>5</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="0">
         <v>1.5</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="0">
         <v>5</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="0" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A7" s="0">
         <v>30006</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0">
         <v>100</v>
       </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="0">
         <v>10</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="0">
         <v>50</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
+      <c r="J7" s="0">
+        <v>1</v>
+      </c>
+      <c r="K7" s="0">
         <v>2</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="L7" s="0">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1424,9 +1419,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" customWidth="1"/>
@@ -1436,111 +1431,111 @@
     <col min="13" max="13" width="15.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="0" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>40001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0">
         <v>100</v>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="0">
         <v>5</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="0">
         <v>5</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
+      <c r="J2" s="0">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="0" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>40002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0">
         <v>100</v>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>5</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="I3" s="0">
+        <v>1</v>
+      </c>
+      <c r="J3" s="0">
+        <v>1</v>
+      </c>
+      <c r="K3" s="0">
+        <v>1</v>
+      </c>
+      <c r="L3" s="0" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1551,33 +1546,33 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.140625" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>50001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>180</v>
       </c>
     </row>
@@ -1589,9 +1584,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12.640625" customWidth="1"/>
@@ -1601,91 +1596,91 @@
     <col min="7" max="7" width="13.92578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>60001</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>30001</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+      <c r="C2" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>60002</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>30002</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="C3" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>60003</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>30003</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
+      <c r="C4" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A5" s="0">
         <v>60004</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>30004</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
+      <c r="C5" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A6" s="0">
         <v>60005</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>30005</v>
       </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
+      <c r="C6" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A7" s="0">
         <v>60006</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>40001</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
+      <c r="C7" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A8" s="0">
         <v>60007</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>40002</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1697,9 +1692,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="13.92578125" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" customWidth="1"/>
@@ -1707,105 +1702,105 @@
     <col min="5" max="5" width="13.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>53</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>70001</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>30001</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>90001</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="0">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>70002</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>30002</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>90002</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="D3" s="0">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>70003</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>30003</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>90003</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
+      <c r="D4" s="0">
+        <v>0</v>
+      </c>
+      <c r="E4" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A5" s="0">
         <v>70004</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>40001</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>100001</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
+      <c r="D5" s="0">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A6" s="0">
         <v>70005</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>40002</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>100002</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="0">
+        <v>0</v>
+      </c>
+      <c r="E6" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1816,33 +1811,33 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.78515625" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>80001</v>
       </c>
     </row>
@@ -1854,9 +1849,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" customWidth="1"/>
@@ -1868,80 +1863,80 @@
     <col min="9" max="9" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="0" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A2" s="0">
         <v>90001</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="G2" s="0">
+        <v>1</v>
+      </c>
+      <c r="I2" s="0">
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A3" s="0">
         <v>90002</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>38</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
+      <c r="G3" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A4" s="0">
         <v>90003</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" s="0">
         <v>0.1</v>
       </c>
     </row>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="88">
   <si>
     <t xml:space="preserve">id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1585,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1615,7 +1615,7 @@
         <v>30001</v>
       </c>
       <c r="C2" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55">
@@ -1667,10 +1667,10 @@
         <v>60006</v>
       </c>
       <c r="B7" s="0">
-        <v>40001</v>
+        <v>30006</v>
       </c>
       <c r="C7" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55">
@@ -1678,9 +1678,20 @@
         <v>60007</v>
       </c>
       <c r="B8" s="0">
+        <v>40001</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A9" s="0">
+        <v>60008</v>
+      </c>
+      <c r="B9" s="0">
         <v>40002</v>
       </c>
-      <c r="C8" s="0">
+      <c r="C9" s="0">
         <v>0</v>
       </c>
     </row>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="850" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="839" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="88">
   <si>
     <t xml:space="preserve">id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1659,7 +1659,7 @@
         <v>30005</v>
       </c>
       <c r="C6" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55">
@@ -1670,7 +1670,7 @@
         <v>30006</v>
       </c>
       <c r="C7" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55">

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="839" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="839" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t xml:space="preserve">id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -258,123 +258,141 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">FireTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FireEffectProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MainTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">메인 기차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LaserProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">target_count</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">CannonProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저격을 발사해 몇 초 후 강한 피해를 준다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t xml:space="preserve">NormalTurretTrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalTurretProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireEffectProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ColdAirProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MainTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">메인 기차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">LaserProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격력이 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포탑들의 체력이 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 골드가 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">적 처치 시 획득하는 경험치가 {0}({1})만큼 증가합니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">전기 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">화면에 있는 다수의 적들을 전기로 공격한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ElectrickProjectile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">target_count</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">포격 포탑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">거대한 미사일을 발사해 몇 초 후 광역 피해를 준다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonTurretTrain</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">CannonProjectile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionRangeTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirRangeTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ElectrickTurretTrain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SniperTurretTrain</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -869,7 +887,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>10</v>
@@ -957,7 +975,7 @@
         <v>44</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55">
@@ -968,7 +986,7 @@
         <v>45</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D2" s="0">
         <v>100</v>
@@ -988,7 +1006,7 @@
         <v>46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D3" s="0">
         <v>200</v>
@@ -1008,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D4" s="0">
         <v>50</v>
@@ -1028,7 +1046,7 @@
         <v>48</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D5" s="0">
         <v>300</v>
@@ -1048,7 +1066,7 @@
         <v>49</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D6" s="0">
         <v>500</v>
@@ -1097,7 +1115,7 @@
         <v>54</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.55">
@@ -1105,7 +1123,7 @@
         <v>20001</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>34</v>
@@ -1117,7 +1135,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1129,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
@@ -1162,7 +1180,7 @@
         <v>54</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H1" s="0" t="s">
         <v>10</v>
@@ -1177,7 +1195,7 @@
         <v>5</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="M1" s="0" t="s">
         <v>55</v>
@@ -1200,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="H2" s="0">
         <v>5</v>
@@ -1218,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="0" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55">
@@ -1238,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
@@ -1256,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55">
@@ -1276,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H4" s="0">
         <v>10</v>
@@ -1294,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55">
@@ -1302,10 +1320,10 @@
         <v>30004</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D5" s="0">
         <v>100</v>
@@ -1314,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H5" s="0">
         <v>15</v>
@@ -1332,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55">
@@ -1340,10 +1358,10 @@
         <v>30005</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D6" s="0">
         <v>100</v>
@@ -1352,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H6" s="0">
         <v>10</v>
@@ -1370,7 +1388,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55">
@@ -1378,10 +1396,10 @@
         <v>30006</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D7" s="0">
         <v>100</v>
@@ -1390,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H7" s="0">
         <v>10</v>
@@ -1408,7 +1426,45 @@
         <v>0</v>
       </c>
       <c r="M7" s="0" t="s">
-        <v>87</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
+      <c r="A8" s="0">
+        <v>30007</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="0">
+        <v>100</v>
+      </c>
+      <c r="E8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="0">
+        <v>15</v>
+      </c>
+      <c r="I8" s="0">
+        <v>50</v>
+      </c>
+      <c r="J8" s="0">
+        <v>1</v>
+      </c>
+      <c r="K8" s="0">
+        <v>7</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0</v>
+      </c>
+      <c r="M8" s="0" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1481,9 @@
   <cols>
     <col min="1" max="2" width="15.640625" customWidth="1"/>
     <col min="3" max="3" width="50.28515625" customWidth="1"/>
-    <col min="4" max="10" width="15.640625" customWidth="1"/>
+    <col min="4" max="5" width="15.640625" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="7" max="10" width="15.640625" customWidth="1"/>
     <col min="11" max="11" width="18.2109375" customWidth="1"/>
     <col min="12" max="12" width="21" customWidth="1"/>
     <col min="13" max="13" width="15.640625" customWidth="1"/>
@@ -1451,7 +1509,7 @@
         <v>54</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H1" s="0" t="s">
         <v>10</v>
@@ -1486,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="H2" s="0">
         <v>5</v>
@@ -1501,7 +1559,7 @@
         <v>5</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55">
@@ -1521,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="H3" s="0">
         <v>5</v>
@@ -1536,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1643,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1659,7 +1717,7 @@
         <v>30005</v>
       </c>
       <c r="C6" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55">
@@ -1678,10 +1736,10 @@
         <v>60007</v>
       </c>
       <c r="B8" s="0">
-        <v>40001</v>
+        <v>30007</v>
       </c>
       <c r="C8" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55">
@@ -1689,9 +1747,20 @@
         <v>60008</v>
       </c>
       <c r="B9" s="0">
+        <v>40001</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55">
+      <c r="A10" s="0">
+        <v>60009</v>
+      </c>
+      <c r="B10" s="0">
         <v>40002</v>
       </c>
-      <c r="C9" s="0">
+      <c r="C10" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1844,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55">
@@ -1888,7 +1957,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F1" s="0" t="s">
         <v>10</v>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -1,30 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" tabRatio="839" firstSheet="2" activeTab="2"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Monster_Data" sheetId="1" r:id="rId4"/>
-    <sheet name="Train_Data" sheetId="2" r:id="rId5"/>
-    <sheet name="Turret_Train_Data" sheetId="3" r:id="rId6"/>
-    <sheet name="Range_Train_Data" sheetId="4" r:id="rId7"/>
-    <sheet name="Stage_Data" sheetId="5" r:id="rId8"/>
-    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId9"/>
-    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId10"/>
-    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId11"/>
-    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId12"/>
-    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId13"/>
-    <sheet name="Upgrade_Data" sheetId="11" r:id="rId14"/>
+    <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Train_Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Range_Train_Data" sheetId="4" r:id="rId3"/>
+    <sheet name="Turret_Train_Data" sheetId="3" r:id="rId4"/>
+    <sheet name="Stage_Data" sheetId="5" r:id="rId5"/>
+    <sheet name="Add_Train_Choice_Data" sheetId="6" r:id="rId6"/>
+    <sheet name="Upgrade_Train_Choice_Data" sheetId="7" r:id="rId7"/>
+    <sheet name="Train_Upgrade_Data" sheetId="8" r:id="rId8"/>
+    <sheet name="Turret_Train_Upgrade_Data" sheetId="9" r:id="rId9"/>
+    <sheet name="Range_Train_Upgrade_Data" sheetId="10" r:id="rId10"/>
+    <sheet name="Upgrade_Data" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr/>
+  <fileRecoveryPr autoRecover="0" crashSave="0" dataExtractLoad="0" repairLoad="0"/>
+  <extLst>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="99">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
@@ -300,6 +306,34 @@
   </si>
   <si>
     <t xml:space="preserve">FireEffectProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">upgrade_type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">NonTrainUpgrade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">TrainUpgrade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">stat_type</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -307,7 +341,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -317,26 +351,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -349,18 +371,11 @@
   </fills>
   <borders count="1">
     <border>
-      <left>
-        <color indexed="64"/>
-      </left>
-      <right>
-        <color indexed="64"/>
-      </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -368,42 +383,28 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf/>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -415,28 +416,20 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="2">
+      <tableStyleElement type="firstColumn" dxfId="1"/>
+      <tableStyleElement type="lastColumn"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
-    </tableStyle>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -725,6 +718,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -732,7 +727,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" style="1" customWidth="1"/>
@@ -746,7 +741,7 @@
     <col min="13" max="13" width="11.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -787,7 +782,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>10001</v>
       </c>
@@ -829,8 +824,9 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -838,7 +834,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="27.5" style="1" customWidth="1"/>
@@ -846,7 +842,7 @@
     <col min="9" max="9" width="19.78515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -875,7 +871,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
@@ -892,7 +888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>100002</v>
       </c>
@@ -910,6 +906,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -918,8 +915,8 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet11"/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="48.5703125" style="1" customWidth="1"/>
@@ -927,9 +924,11 @@
     <col min="5" max="5" width="15.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="18.78515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.78515625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="19.35546875" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -951,8 +950,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="H1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>110001</v>
       </c>
@@ -971,8 +977,14 @@
       <c r="F2" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="H2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>110002</v>
       </c>
@@ -986,13 +998,19 @@
         <v>200</v>
       </c>
       <c r="E3" s="1">
-        <v>-0.10000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="H3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>110003</v>
       </c>
@@ -1011,8 +1029,14 @@
       <c r="F4" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="H4" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A5" s="1">
         <v>110004</v>
       </c>
@@ -1031,8 +1055,11 @@
       <c r="F5" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="H5" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A6" s="1">
         <v>110005</v>
       </c>
@@ -1051,10 +1078,14 @@
       <c r="F6" s="1">
         <v>10</v>
       </c>
+      <c r="H6" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1062,14 +1093,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="46.28515625" style="1" customWidth="1"/>
     <col min="4" max="13" width="15.640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -1092,7 +1123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>20001</v>
       </c>
@@ -1113,6 +1144,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1120,9 +1152,140 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
+  <cols>
+    <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.28515625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="15.640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" style="1" customWidth="1"/>
+    <col min="7" max="10" width="15.640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.2109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.640625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A2" s="1">
+        <v>40001</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="1">
+        <v>100</v>
+      </c>
+      <c r="E2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="1">
+        <v>5</v>
+      </c>
+      <c r="I2" s="1">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
+      <c r="A3" s="1">
+        <v>40002</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>100</v>
+      </c>
+      <c r="E3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="1">
+        <v>5</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="47.92578125" style="1" customWidth="1"/>
@@ -1134,7 +1297,7 @@
     <col min="13" max="13" width="15.640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -1165,8 +1328,8 @@
       <c r="J1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>38</v>
+      <c r="K1" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>44</v>
@@ -1175,7 +1338,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>30001</v>
       </c>
@@ -1204,7 +1367,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>0.29999999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
@@ -1213,7 +1376,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>30002</v>
       </c>
@@ -1242,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1251,7 +1414,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>30003</v>
       </c>
@@ -1289,7 +1452,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A5" s="1">
         <v>30004</v>
       </c>
@@ -1327,7 +1490,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A6" s="1">
         <v>30005</v>
       </c>
@@ -1365,7 +1528,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A7" s="1">
         <v>30006</v>
       </c>
@@ -1403,7 +1566,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A8" s="1">
         <v>30007</v>
       </c>
@@ -1432,7 +1595,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1442,138 +1605,9 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
-  <cols>
-    <col min="1" max="2" width="15.640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.28515625" style="1" customWidth="1"/>
-    <col min="4" max="5" width="15.640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="1" customWidth="1"/>
-    <col min="7" max="10" width="15.640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.2109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="21" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.640625" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1">
-        <v>40001</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" s="1">
-        <v>100</v>
-      </c>
-      <c r="E2" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" s="1">
-        <v>5</v>
-      </c>
-      <c r="I2" s="1">
-        <v>5</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1">
-        <v>40002</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>100</v>
-      </c>
-      <c r="E3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="1">
-        <v>5</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1581,13 +1615,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="21.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -1598,7 +1632,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>50001</v>
       </c>
@@ -1610,6 +1644,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1619,7 +1654,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.640625" style="1" customWidth="1"/>
@@ -1629,7 +1664,7 @@
     <col min="7" max="7" width="13.92578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -1640,7 +1675,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>60001</v>
       </c>
@@ -1648,10 +1683,10 @@
         <v>30001</v>
       </c>
       <c r="C2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>60002</v>
       </c>
@@ -1662,7 +1697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>60003</v>
       </c>
@@ -1673,7 +1708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A5" s="1">
         <v>60004</v>
       </c>
@@ -1684,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A6" s="1">
         <v>60005</v>
       </c>
@@ -1695,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A7" s="1">
         <v>60006</v>
       </c>
@@ -1706,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A8" s="1">
         <v>60007</v>
       </c>
@@ -1714,10 +1749,10 @@
         <v>30007</v>
       </c>
       <c r="C8" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A9" s="1">
         <v>60008</v>
       </c>
@@ -1728,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A10" s="1">
         <v>60009</v>
       </c>
@@ -1740,8 +1775,9 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1749,7 +1785,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="13.92578125" style="1" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" style="1" customWidth="1"/>
@@ -1757,7 +1793,7 @@
     <col min="5" max="5" width="13.78515625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -1774,7 +1810,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>70001</v>
       </c>
@@ -1791,7 +1827,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>70002</v>
       </c>
@@ -1808,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>70003</v>
       </c>
@@ -1825,7 +1861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A5" s="1">
         <v>70004</v>
       </c>
@@ -1842,7 +1878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A6" s="1">
         <v>70005</v>
       </c>
@@ -1860,6 +1896,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -1869,13 +1906,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="15.78515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -1892,12 +1929,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>80001</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1907,7 +1945,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="14.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="32.42578125" style="1" customWidth="1"/>
@@ -1919,7 +1957,7 @@
     <col min="9" max="9" width="16" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -1944,11 +1982,11 @@
       <c r="H1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="I1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
@@ -1962,10 +2000,10 @@
         <v>1</v>
       </c>
       <c r="I2" s="1">
-        <v>0.10000000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
         <v>90002</v>
       </c>
@@ -1979,7 +2017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
         <v>90003</v>
       </c>
@@ -1993,10 +2031,11 @@
         <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>0.10000000000000001</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="5415" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="839" firstSheet="2" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Monster_Data" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="110">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
@@ -98,9 +98,6 @@
     <t xml:space="preserve">weight</t>
   </si>
   <si>
-    <t xml:space="preserve">폭발 포탑</t>
-  </si>
-  <si>
     <t xml:space="preserve">포격 포탑</t>
   </si>
   <si>
@@ -290,13 +287,7 @@
     <t xml:space="preserve">projectile_prefab_id</t>
   </si>
   <si>
-    <t xml:space="preserve">공격력 {0} 증가 범위 {2} 증가</t>
-  </si>
-  <si>
     <t xml:space="preserve">stage_inspection_time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
   </si>
   <si>
     <t xml:space="preserve">레이저로 강하게 지속적인 피해를 준다.</t>
@@ -333,6 +324,62 @@
   </si>
   <si>
     <t xml:space="preserve">AttackInterval</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 범위 {1} 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격하는 적 수 {1} 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격딜레이 {1} 감소</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">공격력 {0} 증가 공격 범위 {1} 증가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">기관총 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미사일 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">레이저 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전기 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">포격 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">저격 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">냉기 포탑 강화</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">폭발 포탑 강화</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -397,29 +444,9 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="2">
-      <tableStyleElement type="firstColumn" dxfId="1"/>
-      <tableStyleElement type="lastColumn"/>
-    </tableStyle>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0"/>
     <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0"/>
   </tableStyles>
   <extLst>
@@ -743,13 +770,13 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -758,28 +785,28 @@
         <v>12</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55">
@@ -799,28 +826,28 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="L2" s="1">
         <v>1.5</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -833,7 +860,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="15.640625" style="1" customWidth="1"/>
@@ -844,13 +871,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -859,30 +886,30 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>100001</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
+      <c r="B2" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
@@ -890,19 +917,88 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
+        <v>100001</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A4" s="1">
+        <v>100001</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A5" s="1">
         <v>100002</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="1">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1</v>
+      <c r="B5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>50</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A6" s="1">
+        <v>100002</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A7" s="1">
+        <v>100002</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -930,31 +1026,31 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="J1" s="2"/>
     </row>
@@ -966,7 +1062,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -978,10 +1074,10 @@
         <v>100</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.55">
@@ -989,7 +1085,7 @@
         <v>110002</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>0</v>
@@ -1004,10 +1100,10 @@
         <v>100</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.55">
@@ -1018,7 +1114,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="1">
         <v>50</v>
@@ -1030,10 +1126,10 @@
         <v>50</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.55">
@@ -1041,7 +1137,7 @@
         <v>110004</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -1056,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.55">
@@ -1064,7 +1160,7 @@
         <v>110005</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -1079,7 +1175,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1102,22 +1198,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -1131,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -1140,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1168,40 +1264,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.55">
@@ -1212,7 +1308,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -1221,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -1236,7 +1332,7 @@
         <v>5</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.55">
@@ -1256,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1">
         <v>5</v>
@@ -1271,7 +1367,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1299,43 +1395,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55">
@@ -1346,7 +1442,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1">
         <v>100</v>
@@ -1355,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H2" s="1">
         <v>5</v>
@@ -1373,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55">
@@ -1384,7 +1480,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" s="1">
         <v>100</v>
@@ -1393,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H3" s="1">
         <v>5</v>
@@ -1411,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55">
@@ -1422,7 +1518,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" s="1">
         <v>100</v>
@@ -1431,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4" s="1">
         <v>10</v>
@@ -1449,7 +1545,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55">
@@ -1460,7 +1556,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
@@ -1469,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H5" s="1">
         <v>15</v>
@@ -1487,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55">
@@ -1498,7 +1594,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
@@ -1507,7 +1603,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
@@ -1525,7 +1621,7 @@
         <v>5</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55">
@@ -1533,7 +1629,7 @@
         <v>30006</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
@@ -1545,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H7" s="1">
         <v>10</v>
@@ -1563,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55">
@@ -1574,7 +1670,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" s="1">
         <v>100</v>
@@ -1583,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H8" s="1">
         <v>10</v>
@@ -1601,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1623,13 +1719,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.55">
@@ -1637,7 +1733,7 @@
         <v>50001</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1">
         <v>180</v>
@@ -1666,10 +1762,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>21</v>
@@ -1784,7 +1880,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="2" max="2" width="13.92578125" style="1" customWidth="1"/>
@@ -1795,13 +1891,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>21</v>
@@ -1866,10 +1962,10 @@
         <v>70004</v>
       </c>
       <c r="B5" s="1">
-        <v>40001</v>
+        <v>30004</v>
       </c>
       <c r="C5" s="1">
-        <v>100001</v>
+        <v>90004</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -1883,22 +1979,90 @@
         <v>70005</v>
       </c>
       <c r="B6" s="1">
+        <v>30005</v>
+      </c>
+      <c r="C6" s="1">
+        <v>90005</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A7" s="1">
+        <v>70006</v>
+      </c>
+      <c r="B7" s="1">
+        <v>30006</v>
+      </c>
+      <c r="C7" s="1">
+        <v>90006</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A8" s="1">
+        <v>70007</v>
+      </c>
+      <c r="B8" s="1">
+        <v>30007</v>
+      </c>
+      <c r="C8" s="1">
+        <v>90007</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A9" s="1">
+        <v>70008</v>
+      </c>
+      <c r="B9" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C9" s="1">
+        <v>100001</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55">
+      <c r="A10" s="1">
+        <v>70009</v>
+      </c>
+      <c r="B10" s="1">
         <v>40002</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C10" s="1">
         <v>100002</v>
       </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1914,13 +2078,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -1944,11 +2108,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="35.0703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" style="1" customWidth="1"/>
@@ -1959,13 +2123,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -1974,69 +2138,351 @@
         <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A2" s="1">
         <v>90001</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>88</v>
+      <c r="B2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I2" s="1">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A3" s="1">
-        <v>90002</v>
-      </c>
-      <c r="B3" s="1" t="s">
+        <v>90001</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="1">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1</v>
+      <c r="I3" s="1">
+        <v>0.05</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55">
       <c r="A4" s="1">
+        <v>90001</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G4" s="1">
+        <v>25</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A5" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A6" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A7" s="1">
+        <v>90002</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A8" s="1">
         <v>90003</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.1</v>
+      <c r="B8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="1">
+        <v>15</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A9" s="1">
+        <v>90003</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="1">
+        <v>20</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A10" s="1">
+        <v>90003</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="1">
+        <v>40</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A11" s="0">
+        <v>90004</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G11" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A12" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A13" s="1">
+        <v>90004</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="1">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A14" s="0">
+        <v>90005</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="1">
+        <v>3</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A15" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55">
+      <c r="A16" s="1">
+        <v>90005</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="1">
+        <v>7</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A17" s="0">
+        <v>90006</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A18" s="1">
+        <v>90006</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A19" s="2">
+        <v>90006</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A20" s="2">
+        <v>90007</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A21" s="2">
+        <v>90007</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G21" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.55">
+      <c r="A22" s="2">
+        <v>90007</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="1">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -903,7 +903,7 @@
         <v>100001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>83</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55">
@@ -920,7 +920,7 @@
         <v>100001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>96</v>
@@ -929,7 +929,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55">
@@ -937,7 +937,7 @@
         <v>100001</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>83</v>
@@ -946,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>2</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55">
@@ -954,7 +954,7 @@
         <v>100002</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>83</v>
@@ -963,7 +963,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2"/>
     </row>
@@ -972,7 +972,7 @@
         <v>100002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>83</v>
@@ -981,7 +981,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55">
@@ -989,7 +989,7 @@
         <v>100002</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>83</v>
@@ -998,13 +998,13 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>250</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Assets/TrainDefenseData.xlsx
+++ b/Assets/TrainDefenseData.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="110">
   <si>
     <t xml:space="preserve">포탑들의 공격 딜레이가 {0}({1})만큼 감소합니다.</t>
   </si>
